--- a/output/pdf_financials_xlsx/SBD.X.xlsx
+++ b/output/pdf_financials_xlsx/SBD.X.xlsx
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -4614,7 +4614,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.0435</v>
       </c>

--- a/output/pdf_financials_xlsx/SBD.X.xlsx
+++ b/output/pdf_financials_xlsx/SBD.X.xlsx
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.000935</v>
+        <v>-0.003471</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.003813</v>
+        <v>0.001383</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-6.3e-05</v>
+        <v>0.002159</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00411</v>
       </c>
     </row>
     <row r="102">
@@ -2581,16 +2581,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.0727</v>
+        <v>0.06829399999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.109897</v>
+        <v>0.115093</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.006963</v>
+        <v>0.009185</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.107682</v>
+        <v>0.103572</v>
       </c>
     </row>
     <row r="107">
@@ -4084,7 +4084,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-0.004406</v>
       </c>
